--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -1869,7 +1869,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Тиль Про, КС.png</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1953,7 +1957,11 @@
           <t>20 л, штабель</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Альфард, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1995,7 +2003,11 @@
           <t>20 л, штабель</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Ампир Экстра, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2037,7 +2049,11 @@
           <t>20 л, штабель</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Ампир, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2079,7 +2095,11 @@
           <t>20 л, штабель</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Ранголи — Ранголи-Базорон, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2121,7 +2141,11 @@
           <t>0,5 кг × 10</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Гекстар, ВДГ.png</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2205,7 +2229,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Злакофф, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2247,7 +2275,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Кирасир, СЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2331,7 +2363,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Клордин, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2373,7 +2409,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Курсар, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2415,7 +2455,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Метолс, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2457,7 +2501,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Поллукс, ЭМВ.png</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2499,7 +2547,11 @@
           <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Спика, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2583,7 +2635,11 @@
           <t>0,5 кг</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Торпеда, ВДГ.png</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2625,7 +2681,11 @@
           <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Укротитель, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4927,7 +4987,11 @@
           <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Альфацин, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -4969,7 +5033,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Гарпун, КС.png</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -5011,7 +5079,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Кастра, КС.png</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -5053,7 +5125,11 @@
           <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Ранголи — Ранголи Норил, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -5095,7 +5171,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Ранголи — Ранголи-Реголон, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -5137,7 +5217,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Ригель Форте, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -5243,7 +5327,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега 90, Ж.png</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -5277,7 +5365,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега АнтиПена, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -5311,7 +5403,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега Баланс, ВР.png</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -5345,7 +5441,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега Голд, Ж.png</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -5413,7 +5513,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега Турбо.png</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -5447,7 +5551,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега Эмульс, КЭ.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Пшеница озимая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Пшеница озимая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Пшеница озимая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Пшеница озимая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Пшеница яровая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Пшеница яровая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Пшеница яровая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Пшеница яровая</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ячмень яровой</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ячмень яровой</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ячмень яровой</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Соя</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Соя</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Соя</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Соя</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Соя</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Соя</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Горох посевной</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Горох посевной</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Гречиха</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Гречиха</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Картофель</t>
+          <t>Сорта</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">

--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -661,7 +661,7 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-1.jpg</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-2.jpg</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-3.jpg</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-1.jpg</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-2.jpg</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-3.jpg</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-1.jpg</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-pshenitsa.jpg</t>
+          <t>seed-crop-pshenitsa-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-yachmen.jpg</t>
+          <t>seed-crop-yachmen-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-yachmen.jpg</t>
+          <t>seed-crop-yachmen-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-yachmen.jpg</t>
+          <t>seed-crop-yachmen-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-soya.jpg</t>
+          <t>seed-crop-soya-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-soya.jpg</t>
+          <t>seed-crop-soya-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-soya.jpg</t>
+          <t>seed-crop-soya-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-soya.jpg</t>
+          <t>seed-crop-soya-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-soya.jpg</t>
+          <t>seed-crop-soya-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>seed-crop-soya.jpg</t>
+          <t>seed-crop-soya-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>seed-crop-goroh-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1483,7 +1487,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>seed-crop-goroh-2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1525,7 +1533,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>seed-crop-grechiha-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1567,7 +1579,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>seed-crop-grechiha-2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1609,7 +1625,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>seed-crop-kartofel-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">

--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>от 585 ₽</t>
+          <t>от 585 ₽/л</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>от 700 ₽</t>
+          <t>от 700 ₽/л</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1475 ₽</t>
+          <t>1475 ₽/л</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>945 ₽</t>
+          <t>945 ₽/л</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1760 ₽</t>
+          <t>1760 ₽/л</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1040 ₽</t>
+          <t>1040 ₽/л</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>540 ₽</t>
+          <t>540 ₽/л</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1040 ₽</t>
+          <t>1040 ₽/л</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2590 ₽</t>
+          <t>2590 ₽/кг</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1825 ₽</t>
+          <t>1825 ₽/л</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>877,5 ₽</t>
+          <t>877,5 ₽/л</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>540 ₽</t>
+          <t>540 ₽/л</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4050 ₽</t>
+          <t>4050 ₽/кг</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1065 ₽</t>
+          <t>1065 ₽/л</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>880 ₽</t>
+          <t>880 ₽/л</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1150 ₽</t>
+          <t>1150 ₽/л</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>745 ₽</t>
+          <t>745 ₽/л</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>850 ₽</t>
+          <t>850 ₽/л</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5625 ₽</t>
+          <t>5625 ₽/кг</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>800 ₽</t>
+          <t>800 ₽/л</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>880 ₽</t>
+          <t>880 ₽/л</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>945 ₽</t>
+          <t>945 ₽/л</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>от 227 ₽</t>
+          <t>от 227 ₽/кг</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>от 202 ₽</t>
+          <t>от 202 ₽/кг</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>от 222 ₽</t>
+          <t>от 222 ₽/кг</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>от 232 ₽</t>
+          <t>от 232 ₽/кг</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>от 225 ₽</t>
+          <t>от 225 ₽/кг</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>от 196 ₽</t>
+          <t>от 196 ₽/кг</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>от 207 ₽</t>
+          <t>от 207 ₽/кг</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>от 203 ₽</t>
+          <t>от 203 ₽/кг</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>от 112 ₽</t>
+          <t>от 112 ₽/кг</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3273,7 +3273,7 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>от 96 ₽</t>
+          <t>от 96 ₽/кг</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>от 106 ₽</t>
+          <t>от 106 ₽/кг</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>от 110 ₽</t>
+          <t>от 110 ₽/кг</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>от 48 ₽ (МКР) · 54 ₽ (25 кг)</t>
+          <t>от 48 ₽/кг (МКР) · 54 ₽/кг (25 кг)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>от 103 ₽ (МКР 1000 кг) · 108 ₽ (мешки 35 кг)</t>
+          <t>от 103 ₽/кг (МКР 1000 кг) · 108 ₽/кг (мешки 35 кг)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>от 97 ₽</t>
+          <t>от 97 ₽/кг</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>от 595 ₽</t>
+          <t>от 595 ₽/л</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>от 315 ₽</t>
+          <t>от 315 ₽/л</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>от 535 ₽</t>
+          <t>от 535 ₽/л</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>от 315 ₽</t>
+          <t>от 315 ₽/л</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>от 450 ₽</t>
+          <t>от 450 ₽/л</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>от 635 ₽</t>
+          <t>от 635 ₽/л</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>от 500 ₽</t>
+          <t>от 500 ₽/л</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>от 400 ₽</t>
+          <t>от 400 ₽/л</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>от 545 ₽</t>
+          <t>от 545 ₽/л</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>от 1470 ₽</t>
+          <t>от 1470 ₽/л</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>от 685 ₽</t>
+          <t>от 685 ₽/л</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>от 670 ₽</t>
+          <t>от 670 ₽/л</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>от 455 ₽</t>
+          <t>от 455 ₽/л</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>от 510 ₽</t>
+          <t>от 510 ₽/л</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>от 800 ₽</t>
+          <t>от 800 ₽/л</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4493,7 +4493,7 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>от 1245 ₽</t>
+          <t>от 1245 ₽/л</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>1562,5 ₽</t>
+          <t>1562,5 ₽/л</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1417,5 ₽</t>
+          <t>1417,5 ₽/л</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>510 ₽</t>
+          <t>510 ₽/л</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>1150 ₽</t>
+          <t>1150 ₽/л</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>1125 ₽</t>
+          <t>1125 ₽/л</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1040 ₽</t>
+          <t>1040 ₽/л</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>392 ₽</t>
+          <t>392 ₽/л</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>540 ₽</t>
+          <t>540 ₽/л</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">

--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>от 735 ₽</t>
+          <t>от 735 ₽/л</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>от 615 ₽</t>
+          <t>от 615 ₽/л</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>от 1340 ₽</t>
+          <t>от 1340 ₽/л</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>от 730 ₽</t>
+          <t>от 730 ₽/л</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>от 765 ₽</t>
+          <t>от 765 ₽/л</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>от 695 ₽</t>
+          <t>от 695 ₽/л</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>от 470 ₽</t>
+          <t>от 470 ₽/л</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>от 700 ₽ (рассрочка 735 ₽)</t>
+          <t>от 700 ₽/л (рассрочка 735 ₽/л)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>от 635 ₽ (рассрочка 730 ₽)</t>
+          <t>от 635 ₽/л (рассрочка 730 ₽/л)</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5343,7 +5343,7 @@
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>от 220 ₽ (рассрочка 253 ₽)</t>
+          <t>от 220 ₽/л (рассрочка 253 ₽/л)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5457,7 +5457,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>от 1350 ₽ (рассрочка 1552,5 ₽)</t>
+          <t>от 1350 ₽/л (рассрочка 1552,5 ₽/л)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>от 426 ₽ (рассрочка 490 ₽)</t>
+          <t>от 426 ₽/л (рассрочка 490 ₽/л)</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>

--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -1763,7 +1763,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Реликт ДВ — Реликт Р Старт (протравитель).png</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1805,7 +1809,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Анкер Трио, КС.png</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1847,7 +1855,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Тиара, КС.png</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1935,7 +1947,11 @@
           <t>5 л × 4</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Тореадор Макси, КС.png</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2341,7 +2357,11 @@
           <t>1 кг × 10</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Клео, ВДГ.png</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2613,7 +2633,11 @@
           <t>0,1 кг × 100</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Тифилагро, ВДГ.png</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2747,7 +2771,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Царумин, ВК.png</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2789,7 +2817,11 @@
           <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Челленджер, ВРК.png</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3657,7 +3689,11 @@
           <t>водорастворимые гранулы, 800 кг</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA — Газонное. Осень.png</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4923,7 +4959,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Гранберг Про, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -4965,7 +5005,11 @@
           <t>10 л × 2</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Гранберг, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -5313,7 +5357,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Биостик Терра.png</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">

--- a/catalogs/Saturn-каталог-для-сайта.xlsx
+++ b/catalogs/Saturn-каталог-для-сайта.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>от 585 ₽/л</t>
+          <t>от 645,7 ₽/л</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>от 700 ₽/л</t>
+          <t>от 724,5 ₽/л</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>800 кг</t>
+          <t>800 кг, 40 кг</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>800 кг</t>
+          <t>800 кг, 40 кг</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>800 кг</t>
+          <t>800 кг, 40 кг</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>800 кг</t>
+          <t>800 кг, 40 кг</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>от 595 ₽/л</t>
+          <t>от 651 ₽/л</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>от 651 ₽</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>от 315 ₽/л</t>
+          <t>от 409,5 ₽/л</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>от 535 ₽/л</t>
+          <t>от 577,5 ₽/л</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>от 315 ₽/л</t>
+          <t>от 332,5 ₽/л</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>от 450 ₽/л</t>
+          <t>от 490 ₽/л</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>от 635 ₽/л</t>
+          <t>от 760 ₽/л</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>от 500 ₽/л</t>
+          <t>от 728 ₽/л</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>от 400 ₽/л</t>
+          <t>от 430 ₽/л</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>от 545 ₽/л</t>
+          <t>от 465 ₽/л</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>от 1470 ₽/л</t>
+          <t>от 1290 ₽/л</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>от 685 ₽/л</t>
+          <t>от 650 ₽/л</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>от 670 ₽/л</t>
+          <t>от 653 ₽/л</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>от 455 ₽/л</t>
+          <t>от 520 ₽/л</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>от 510 ₽/л</t>
+          <t>от 605 ₽/л</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>от 1290 ₽</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>от 800 ₽/л</t>
+          <t>от 695 ₽/л</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4529,7 +4529,7 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>от 1245 ₽/л</t>
+          <t>от 1020 ₽/л</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4841,38 +4841,38 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Удобрения и листовые подкормки</t>
+          <t>Фунгициды</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Фунгициды</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Волски Аминатор</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Волски Биохим</t>
-        </is>
-      </c>
+          <t>Атлант Супер</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Волски Биохим · листовые подкормки</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
+          <t>пропиконазол 250 г/л + ципроконазол 80 г/л</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница, Свёкла</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>от 900 ₽</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>раствор</t>
+          <t>5 л × 4</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -4893,31 +4893,35 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Атлант Супер</t>
+          <t>Гранберг Про, КЭ</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>пропиконазол 250 г/л + ципроконазол 80 г/л</t>
+          <t>пропиконазол 300 г/л + тебуконазол 200 г/л</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Свёкла</t>
+          <t>Пшеница, Ячмень, Рапс, Соя, Свёкла</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>1562,5 ₽/л</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>5 л × 4</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr"/>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>СЗР — Гранберг Про, КЭ.png</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -4935,23 +4939,23 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Гранберг Про, КЭ</t>
+          <t>Гранберг, КЭ</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>пропиконазол 300 г/л + тебуконазол 200 г/л</t>
+          <t>тебуконазол 250 г/л</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Ячмень, Рапс, Соя, Свёкла</t>
+          <t>Пшеница, Ячмень, Рапс</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>1562,5 ₽/л</t>
+          <t>1417,5 ₽/л</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4961,7 +4965,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>СЗР — Гранберг Про, КЭ.png</t>
+          <t>СЗР — Гранберг, КЭ.png</t>
         </is>
       </c>
     </row>
@@ -4971,43 +4975,43 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Фунгициды</t>
+          <t>Инсектициды</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Фунгициды</t>
+          <t>Инсектициды</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Гранберг, КЭ</t>
+          <t>Альфацин, КЭ</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>тебуконазол 250 г/л</t>
+          <t>альфа-циперметрин 100 г/л</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Ячмень, Рапс</t>
+          <t>Пшеница, Ячмень, Рапс, Картофель, Свёкла, Горох</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1417,5 ₽/л</t>
+          <t>510 ₽/л</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>10 л × 2</t>
+          <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>СЗР — Гранберг, КЭ.png</t>
+          <t>НПК Химия — Альфацин, КЭ.png</t>
         </is>
       </c>
     </row>
@@ -5027,33 +5031,33 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Альфацин, КЭ</t>
+          <t>Гарпун, КС</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>альфа-циперметрин 100 г/л</t>
+          <t>ацетамиприд 115 г/л + лямбда-цигалотрин 106 г/л</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Ячмень, Рапс, Картофель, Свёкла, Горох</t>
+          <t>Пшеница, Ячмень, Рапс, Соя, Свёкла, Горох</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>510 ₽/л</t>
+          <t>1150 ₽/л</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>5 л × 4; 10 л × 2</t>
+          <t>5 л × 4</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Альфацин, КЭ.png</t>
+          <t>НПК Химия — Гарпун, КС.png</t>
         </is>
       </c>
     </row>
@@ -5073,23 +5077,23 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Гарпун, КС</t>
+          <t>Кастра, КС</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>ацетамиприд 115 г/л + лямбда-цигалотрин 106 г/л</t>
+          <t>клотианидин 140 г/л + лямбда-цигалотрин 100 г/л</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Ячмень, Рапс, Соя, Свёкла, Горох</t>
+          <t>Пшеница, Ячмень, Рапс, Соя</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>1150 ₽/л</t>
+          <t>1125 ₽/л</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5099,7 +5103,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Гарпун, КС.png</t>
+          <t>НПК Химия — Кастра, КС.png</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5123,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Кастра, КС</t>
+          <t>Ранголи Норил, КЭ</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5130,22 +5134,22 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Ячмень, Рапс, Соя</t>
+          <t>Пшеница, Ячмень, Рапс</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>1125 ₽/л</t>
+          <t>1040 ₽/л</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>5 л × 4</t>
+          <t>5 л × 4; 10 л × 2</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Кастра, КС.png</t>
+          <t>Ранголи — Ранголи Норил, КЭ.png</t>
         </is>
       </c>
     </row>
@@ -5155,43 +5159,43 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Инсектициды</t>
+          <t>Десиканты</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Инсектициды</t>
+          <t>Десиканты</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Ранголи Норил, КЭ</t>
+          <t>Ранголи-Реголон, ВР</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>клотианидин 140 г/л + лямбда-цигалотрин 100 г/л</t>
+          <t>дикват дибромид 150 г/л (пересчёт на дикват-ион 80,3 г/л)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Пшеница, Ячмень, Рапс</t>
+          <t>Подсолнечник</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1040 ₽/л</t>
+          <t>392 ₽/л</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>5 л × 4; 10 л × 2</t>
+          <t>10 л × 2</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Ранголи — Ранголи Норил, КЭ.png</t>
+          <t>Ранголи — Ранголи-Реголон, ВР.png</t>
         </is>
       </c>
     </row>
@@ -5211,23 +5215,23 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Ранголи-Реголон, ВР</t>
+          <t>Ригель Форте, ВР</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>дикват дибромид 150 г/л (пересчёт на дикват-ион 80,3 г/л)</t>
+          <t>дикват дибромид 240 г/л (пересчёт на дикват-ион 128 г/л)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Подсолнечник</t>
+          <t>Рапс, Подсолнечник, Соя, Картофель, Горох</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>392 ₽/л</t>
+          <t>540 ₽/л</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5237,7 +5241,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Ранголи — Ранголи-Реголон, ВР.png</t>
+          <t>НПК Химия — Ригель Форте, ВР.png</t>
         </is>
       </c>
     </row>
@@ -5247,43 +5251,35 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Десиканты</t>
+          <t>Адъюванты</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Десиканты</t>
+          <t>Адъюванты</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Ригель Форте, ВР</t>
+          <t>Волски Оптим</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>дикват дибромид 240 г/л (пересчёт на дикват-ион 128 г/л)</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Рапс, Подсолнечник, Соя, Картофель, Горох</t>
-        </is>
-      </c>
+          <t>рН-корректор рабочего раствора</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>540 ₽/л</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>10 л × 2</t>
-        </is>
-      </c>
+          <t>от 700 ₽/л (рассрочка 735 ₽/л)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Ригель Форте, ВР.png</t>
+          <t>Волски Биохим — Корректор рН «ВОЛСКИ ОПТИМ».png</t>
         </is>
       </c>
     </row>
@@ -5303,25 +5299,25 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Волски Оптим</t>
+          <t>Биостик Терра</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>рН-корректор рабочего раствора</t>
+          <t>Биоклей для гороха, сои, чечевицы, рапса, льна, горчицы</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>от 700 ₽/л (рассрочка 735 ₽/л)</t>
+          <t>от 635 ₽/л (рассрочка 730 ₽/л)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Волски Биохим — Корректор рН «ВОЛСКИ ОПТИМ».png</t>
+          <t>СЗР — Биостик Терра.png</t>
         </is>
       </c>
     </row>
@@ -5341,25 +5337,25 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Биостик Терра</t>
+          <t>Вега 90, Ж</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Биоклей для гороха, сои, чечевицы, рапса, льна, горчицы</t>
+          <t>ПАВ-адъювант для совместного применения с эмульсионными гербицидами</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>от 635 ₽/л (рассрочка 730 ₽/л)</t>
+          <t>от 220 ₽/кг (рассрочка 253 ₽/кг)</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>СЗР — Биостик Терра.png</t>
+          <t>НПК Химия — Вега 90, Ж.png</t>
         </is>
       </c>
     </row>
@@ -5379,25 +5375,25 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Вега 90, Ж</t>
+          <t>Вега АнтиПена, КЭ</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>ПАВ-адъювант для совместного применения с эмульсионными гербицидами</t>
+          <t>Пеногаситель для баковых смесей пестицидов</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>от 220 ₽/л (рассрочка 253 ₽/л)</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Вега 90, Ж.png</t>
+          <t>НПК Химия — Вега АнтиПена, КЭ.png</t>
         </is>
       </c>
     </row>
@@ -5417,13 +5413,13 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Вега АнтиПена, КЭ</t>
+          <t>Вега Баланс, ВР</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Пеногаситель для баковых смесей пестицидов</t>
+          <t>Кондиционер и смягчитель воды под физиологически кислые пестициды</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -5435,7 +5431,7 @@
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Вега АнтиПена, КЭ.png</t>
+          <t>НПК Химия — Вега Баланс, ВР.png</t>
         </is>
       </c>
     </row>
@@ -5455,25 +5451,25 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Вега Баланс, ВР</t>
+          <t>Вега Голд, Ж</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер и смягчитель воды под физиологически кислые пестициды</t>
+          <t>Кремнийорганический ПАВ-адъювант, суперсмачиватель</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>от 1350 ₽/кг (рассрочка 1552,5 ₽/кг)</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>НПК Химия — Вега Баланс, ВР.png</t>
+          <t>НПК Химия — Вега Голд, Ж.png</t>
         </is>
       </c>
     </row>
@@ -5493,27 +5489,23 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Вега Голд, Ж</t>
+          <t>Вега Клей</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Кремнийорганический ПАВ-адъювант, суперсмачиватель</t>
+          <t>Клей для крестоцветных и зернобобовых — против опадения и потери зерна</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>от 1350 ₽/л (рассрочка 1552,5 ₽/л)</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>НПК Химия — Вега Голд, Ж.png</t>
-        </is>
-      </c>
+      <c r="J110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -5531,23 +5523,27 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Вега Клей</t>
+          <t>Вега Турбо</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Клей для крестоцветных и зернобобовых — против опадения и потери зерна</t>
+          <t>Чистящее средство для промывки опрыскивающего оборудования</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>от 426 ₽/кг (рассрочка 490 ₽/кг)</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>НПК Химия — Вега Турбо.png</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -5565,61 +5561,23 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Вега Турбо</t>
+          <t>Вега Эмульс, КЭ</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Чистящее средство для промывки опрыскивающего оборудования</t>
+          <t>ПАВ-адъювант для повышения эффективности СЗР</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>от 426 ₽/л (рассрочка 490 ₽/л)</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>НПК Химия — Вега Турбо.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Адъюванты</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Адъюванты</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Вега Эмульс, КЭ</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>ПАВ-адъювант для повышения эффективности СЗР</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>НПК Химия — Вега Эмульс, КЭ.png</t>
         </is>
